--- a/Kachi_Gun/Table/Supply.xlsx
+++ b/Kachi_Gun/Table/Supply.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -507,6 +507,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -575,6 +576,11 @@
           <t>Cum_Boss_Dmg (%)</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -620,6 +626,11 @@
       <c r="M2" s="8" t="n">
         <v>3</v>
       </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>supply_01</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -665,6 +676,11 @@
       <c r="M3" s="8" t="n">
         <v>7.5</v>
       </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>supply_02</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -710,6 +726,11 @@
       <c r="M4" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>supply_03</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -755,6 +776,11 @@
       <c r="M5" s="3" t="n">
         <v>21</v>
       </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>supply_04</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -800,6 +826,11 @@
       <c r="M6" s="3" t="n">
         <v>30</v>
       </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>supply_05</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -845,6 +876,11 @@
       <c r="M7" s="3" t="n">
         <v>40.5</v>
       </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>supply_06</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -890,6 +926,11 @@
       <c r="M8" s="3" t="n">
         <v>52.5</v>
       </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>supply_07</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -935,6 +976,11 @@
       <c r="M9" s="3" t="n">
         <v>66</v>
       </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>supply_08</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -980,6 +1026,11 @@
       <c r="M10" s="3" t="n">
         <v>81</v>
       </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>supply_09</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -1025,6 +1076,11 @@
       <c r="M11" s="3" t="n">
         <v>97.5</v>
       </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>supply_10</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1070,6 +1126,11 @@
       <c r="M12" s="3" t="n">
         <v>115.5</v>
       </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>supply_11</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1115,6 +1176,11 @@
       <c r="M13" s="3" t="n">
         <v>135</v>
       </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>supply_12</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1160,6 +1226,11 @@
       <c r="M14" s="3" t="n">
         <v>156</v>
       </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>supply_13</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1205,6 +1276,11 @@
       <c r="M15" s="3" t="n">
         <v>178.5</v>
       </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>supply_14</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -1250,6 +1326,11 @@
       <c r="M16" s="3" t="n">
         <v>202.5</v>
       </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>supply_15</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1295,6 +1376,11 @@
       <c r="M17" s="3" t="n">
         <v>228</v>
       </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>supply_16</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -1340,6 +1426,11 @@
       <c r="M18" s="3" t="n">
         <v>255</v>
       </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>supply_17</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1385,6 +1476,11 @@
       <c r="M19" s="3" t="n">
         <v>283.5</v>
       </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>supply_18</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1430,6 +1526,11 @@
       <c r="M20" s="3" t="n">
         <v>313.5</v>
       </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>supply_19</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1475,6 +1576,11 @@
       <c r="M21" s="3" t="n">
         <v>345</v>
       </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>supply_20</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -1520,6 +1626,11 @@
       <c r="M22" s="3" t="n">
         <v>378</v>
       </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>supply_21</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1565,6 +1676,11 @@
       <c r="M23" s="3" t="n">
         <v>412.5</v>
       </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>supply_22</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -1610,6 +1726,11 @@
       <c r="M24" s="3" t="n">
         <v>448.5</v>
       </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>supply_23</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1655,6 +1776,11 @@
       <c r="M25" s="3" t="n">
         <v>486</v>
       </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>supply_24</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -1699,6 +1825,11 @@
       </c>
       <c r="M26" s="3" t="n">
         <v>525</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>supply_25</t>
+        </is>
       </c>
     </row>
   </sheetData>
